--- a/民事/小恩/案件資訊/C20250001_小恩_案件資訊.xlsx
+++ b/民事/小恩/案件資訊/C20250001_小恩_案件資訊.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="詳細資訊" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="基本資訊" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進度歷史" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進度階段" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>678</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>三審</t>
+          <t>二審</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-06-25 12:51:58</t>
+          <t>2025-06-25 13:51:54</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>進度</t>
+          <t>進度階段</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -677,36 +677,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一審</t>
+          <t>二審</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>二審</t>
+          <t>三審</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>三審</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-06-30</t>
+          <t>2025-07-02</t>
         </is>
       </c>
     </row>
